--- a/human_validation/judge/kor/judge_D008_S004_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D008_S004_P003__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,439 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 저는 [이름] 선생님입니다, 만나서 반갑습니다. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 주로, 잠을 자도 안 풀리는 그런 피로감 때문에 왔어요. 식기세척기 정리하거나 자격증 수업 자료 읽는 것 같은 작은 일들도 너무 과하게 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 상태가 얼마나 오래되셨어요? 몇 주 정도인가요, 아니면 몇 달째인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 한 4개월 정도 된 것 같아요. 남편이랑 말다툼이 훨씬 잦아졌을 때쯤부터 시작된 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 지난 4개월 동안 예전에 즐기시던 활동들에 흥미나 즐거움이 줄어든 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 평소에 저다운 느낌을 주던 것들—스케치, 갤러리 오프닝, 요리, 요가, 친구랑 테니스 치는 것까지—에 대해 관심이 좀 없어졌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 밤에 충분히 주무신 날에도 일어나면 여전히 지치거나 개운하지 않은 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 밤새 푹 자도, 일어나면 제대로 쉬지 못한 느낌이에요. 식기세척기 정리하거나 수업 자료 읽으려는 것 같은 작은 일들도 너무 과하게 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 주무실 때 크게 코를 곤다거나, 숨이 멎거나 헐떡이는 것 같다고 누가 말씀하신 적 있으세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 아무도 그런 말을 해준 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 지난 4개월 동안 의도치 않게 체중이 늘거나 줄었던 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 일부러 뺀 건 아닌데 살이 좀 빠진 것 같아요. 식욕이 좀 이상해졌는데, 하루 종일 커피랑 몇 입 먹은 게 다인 날도 있고, 청바지도 헐렁해졌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 지난 몇 달 동안 평소보다 유난히 목이 마르거나 소변을 자주 보게 된 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 평소보다 목이 더 마르거나 화장실을 더 자주 가게 된 건 딱히 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 지난 4개월 동안 평소와 달리 죄책감이 들거나, 자신이 가치 없거나 다른 사람들에게 짐이 된다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 죄책감이 들거나 제가 가치 없거나 짐이 된다는 느낌은 딱히 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 지난 4개월 동안 여러 가지 일들에 대해 과도하게 걱정하게 되셨나요? 그리고 그 걱정을 통제하거나 멈출 수 없다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 멈출 수 없는 걱정을 많이 한다고는 딱히 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 지난 4개월 동안 거의 매일 하루의 대부분 동안 슬프거나 가라앉거나 절망적인 기분이 드셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 잘 모르겠어요. 대부분의 날에 기분이 가라앉거나 절망적이라고는 딱히 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 지난 몇 달 동안, 특히 몸을 움직일 때 평소와 달리 숨이 차거나 어지럽거나 아찔한 느낌을 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 잘 모르겠어요—그런 건 딱히 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 본인이나 다른 사람이, 피부나 입술, 손톱 밑이 평소와 달리 창백해 보인다고 느끼신 적이 있나요? 아니면 예전보다 추위를 더 자주 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 아니요, 피부나 입술이 창백해 보인다고는 못 느꼈고, 평소보다 더 춥다고 느낀 것 같지도 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 밤에 충분히 주무셨는데도 낮에 낮잠이 필요하거나 활동 중에 깨어 있기 힘드신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 네, 가끔요. 잠을 잤는데도 여전히 정말 피곤해요—식기세척기 정리하거나 자격증 수업 자료 읽으려는 것 같은 작은 일들도 너무 과하게 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 지난 4개월 동안 평소보다 집중하거나, 명확하게 생각하거나, 결정을 내리는 게 더 힘들어진 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 네, 그런 것 같아요. 일정 관리 앱을 열어놓고 그냥 멍하니 보게 돼요—수업 과제를 할지, 청구서를 낼지, 저녁을 시작할지 결정을 못 하고요. 그러다 결국 한동안 아무것도 안 하게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 이번 일 이전에도, 이렇게 지치고 의욕이 없고 평소에 즐기던 것들에 흥미가 없었던 시기가 몇 주나 몇 달간 있었던 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 네. 예전에도 평소에 저다운 느낌을 주던 것들—스케치, 갤러리 오프닝 가기, 요리, 요가, 친구랑 테니스 치는 것까지—에 대한 관심이 사라졌던 시기가 있었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 그 예전 시기들과 지금 사이에, 몇 주나 몇 달 동안 원래 모습으로 돌아왔던 적이 있나요, 아니면 이 가라앉고 지친 느낌이 어느 정도는 항상 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 잘 모르겠어요. 좀 더 저다운 느낌이 들었던 시기가 있었던 건 아는데, 그게 정확히 얼마나 지속됐는지는 말씀드리기 어려워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 말씀하신 그 예전 시기를 떠올려 보시면, 적어도 2주 이상 지속됐는지 기억나세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 며칠 안 좋았던 정도보다는 길었던 걸로 기억하는데, 그게 2주였는지 그보다 길었는지는 확실히 말씀드리기 어려워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 낮에 낮잠을 주무시면, 일어났을 때 개운하신가요, 아니면 자기 전이랑 똑같이 피곤하신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 여전히 피곤해요, 정말로요. 낮잠을 자도 안 풀리는 것 같아요. 자고 난 뒤에도 식기세척기 정리하거나 자격증 수업 자료 읽으려는 것 같은 작은 일이 너무 과하게 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 보통 하룻밤에 총 몇 시간 정도 주무세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 정확히는 잘 모르겠어요. 보통 하룻밤에 몇 시간 자는지 딱히 기록해 놓지 않았거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 예전보다 눈에 띄게 잠을 더 많이 주무시나요? 예를 들어 낮잠 포함해서 24시간 중 9~10시간 이상이요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 정말 뭐라 말씀드리기 어려워요. 하루에 그 정도까지 되는지 딱히 눈치채거나 기록해 놓지 않았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 제1형 양극성장애 (D008)
 인구통계: 성별 여성 / 나이 33 / 직업상태 no occupation / 최종학력 대학 재학
@@ -575,497 +999,46 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S029
-배경 서술: 실비아의 어려움은 예산 문제, 집안 살림, 그리고 미술치료 자격증 과정과 지역사회 미술 프로젝트에 쏟는 시간을 두고 배우자와의 말다툼이 급격히 늘어난 시기에 눈에 띄기 시작했다. 처음에 그녀는 그 긴장을 더 큰 뉴스레터, 새로운 갤러리 파트너십, 프리랜서 컨설팅 사업 시작이라는 야심 찬 계획으로 돌렸지만, 4개월에 걸쳐 고양되고 예민한 기분, 빠르게 몰아치는 말, 질주하는 생각들, 늘어난 활동량이 수업과 가정에서의 책임, 그리고 의사결정 능력에 지장을 주기 시작했다. 이후 이어진 우울 국면은 좀 더 조용했지만 여전히 기능을 저해했다. 그녀는 갤러리 방문, 스케치, 요리, 요가, 테니스에 흥미를 잃었고, 식욕과 체중 변화를 겪었으며, 지속적인 피로감을 느꼈고, 집중력 저하와 정신운동 지연으로 힘들어했다. 그녀는 상세한 일기와 일정 관리 앱을 계속 기록해 왔기에 스스로 이 패턴을 알아챘고, 부부간의 갈등이나 기능적 문제가 더 악화되기 전에 담당 치료사를 통해 외래 정신건강의학과 의뢰를 요청했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 저는 [이름] 선생님입니다, 만나서 반갑습니다. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 주로, 잠을 자도 안 풀리는 그런 피로감 때문에 왔어요. 식기세척기 정리하거나 자격증 수업 자료 읽는 것 같은 작은 일들도 너무 과하게 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 상태가 얼마나 오래되셨어요? 몇 주 정도인가요, 아니면 몇 달째인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 한 4개월 정도 된 것 같아요. 남편이랑 말다툼이 훨씬 잦아졌을 때쯤부터 시작된 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 지난 4개월 동안 예전에 즐기시던 활동들에 흥미나 즐거움이 줄어든 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 평소에 저다운 느낌을 주던 것들—스케치, 갤러리 오프닝, 요리, 요가, 친구랑 테니스 치는 것까지—에 대해 관심이 좀 없어졌어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 밤에 충분히 주무신 날에도 일어나면 여전히 지치거나 개운하지 않은 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 밤새 푹 자도, 일어나면 제대로 쉬지 못한 느낌이에요. 식기세척기 정리하거나 수업 자료 읽으려는 것 같은 작은 일들도 너무 과하게 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 주무실 때 크게 코를 곤다거나, 숨이 멎거나 헐떡이는 것 같다고 누가 말씀하신 적 있으세요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 아무도 그런 말을 해준 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 지난 4개월 동안 의도치 않게 체중이 늘거나 줄었던 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 일부러 뺀 건 아닌데 살이 좀 빠진 것 같아요. 식욕이 좀 이상해졌는데, 하루 종일 커피랑 몇 입 먹은 게 다인 날도 있고, 청바지도 헐렁해졌어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 지난 몇 달 동안 평소보다 유난히 목이 마르거나 소변을 자주 보게 된 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 평소보다 목이 더 마르거나 화장실을 더 자주 가게 된 건 딱히 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 지난 4개월 동안 평소와 달리 죄책감이 들거나, 자신이 가치 없거나 다른 사람들에게 짐이 된다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 죄책감이 들거나 제가 가치 없거나 짐이 된다는 느낌은 딱히 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 지난 4개월 동안 여러 가지 일들에 대해 과도하게 걱정하게 되셨나요? 그리고 그 걱정을 통제하거나 멈출 수 없다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 멈출 수 없는 걱정을 많이 한다고는 딱히 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 지난 4개월 동안 거의 매일 하루의 대부분 동안 슬프거나 가라앉거나 절망적인 기분이 드셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 잘 모르겠어요. 대부분의 날에 기분이 가라앉거나 절망적이라고는 딱히 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 지난 몇 달 동안, 특히 몸을 움직일 때 평소와 달리 숨이 차거나 어지럽거나 아찔한 느낌을 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 잘 모르겠어요—그런 건 딱히 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 본인이나 다른 사람이, 피부나 입술, 손톱 밑이 평소와 달리 창백해 보인다고 느끼신 적이 있나요? 아니면 예전보다 추위를 더 자주 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 아니요, 피부나 입술이 창백해 보인다고는 못 느꼈고, 평소보다 더 춥다고 느낀 것 같지도 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 밤에 충분히 주무셨는데도 낮에 낮잠이 필요하거나 활동 중에 깨어 있기 힘드신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 네, 가끔요. 잠을 잤는데도 여전히 정말 피곤해요—식기세척기 정리하거나 자격증 수업 자료 읽으려는 것 같은 작은 일들도 너무 과하게 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 지난 4개월 동안 평소보다 집중하거나, 명확하게 생각하거나, 결정을 내리는 게 더 힘들어진 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 네, 그런 것 같아요. 일정 관리 앱을 열어놓고 그냥 멍하니 보게 돼요—수업 과제를 할지, 청구서를 낼지, 저녁을 시작할지 결정을 못 하고요. 그러다 결국 한동안 아무것도 안 하게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 이번 일 이전에도, 이렇게 지치고 의욕이 없고 평소에 즐기던 것들에 흥미가 없었던 시기가 몇 주나 몇 달간 있었던 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 네. 예전에도 평소에 저다운 느낌을 주던 것들—스케치, 갤러리 오프닝 가기, 요리, 요가, 친구랑 테니스 치는 것까지—에 대한 관심이 사라졌던 시기가 있었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 그 예전 시기들과 지금 사이에, 몇 주나 몇 달 동안 원래 모습으로 돌아왔던 적이 있나요, 아니면 이 가라앉고 지친 느낌이 어느 정도는 항상 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 잘 모르겠어요. 좀 더 저다운 느낌이 들었던 시기가 있었던 건 아는데, 그게 정확히 얼마나 지속됐는지는 말씀드리기 어려워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 말씀하신 그 예전 시기를 떠올려 보시면, 적어도 2주 이상 지속됐는지 기억나세요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 며칠 안 좋았던 정도보다는 길었던 걸로 기억하는데, 그게 2주였는지 그보다 길었는지는 확실히 말씀드리기 어려워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 낮에 낮잠을 주무시면, 일어났을 때 개운하신가요, 아니면 자기 전이랑 똑같이 피곤하신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 여전히 피곤해요, 정말로요. 낮잠을 자도 안 풀리는 것 같아요. 자고 난 뒤에도 식기세척기 정리하거나 자격증 수업 자료 읽으려는 것 같은 작은 일이 너무 과하게 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 보통 하룻밤에 총 몇 시간 정도 주무세요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 정확히는 잘 모르겠어요. 보통 하룻밤에 몇 시간 자는지 딱히 기록해 놓지 않았거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 예전보다 눈에 띄게 잠을 더 많이 주무시나요? 예를 들어 낮잠 포함해서 24시간 중 9~10시간 이상이요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 정말 뭐라 말씀드리기 어려워요. 하루에 그 정도까지 되는지 딱히 눈치채거나 기록해 놓지 않았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 실비아의 어려움은 예산 문제, 집안 살림, 그리고 미술치료 자격증 과정과 지역사회 미술 프로젝트에 쏟는 시간을 두고 배우자와의 말다툼이 급격히 늘어난 시기에 눈에 띄기 시작했다. 처음에 그녀는 그 긴장을 더 큰 뉴스레터, 새로운 갤러리 파트너십, 프리랜서 컨설팅 사업 시작이라는 야심 찬 계획으로 돌렸지만, 4개월에 걸쳐 고양되고 예민한 기분, 빠르게 몰아치는 말, 질주하는 생각들, 늘어난 활동량이 수업과 가정에서의 책임, 그리고 의사결정 능력에 지장을 주기 시작했다. 이후 이어진 우울 국면은 좀 더 조용했지만 여전히 기능을 저해했다. 그녀는 갤러리 방문, 스케치, 요리, 요가, 테니스에 흥미를 잃었고, 식욕과 체중 변화를 겪었으며, 지속적인 피로감을 느꼈고, 집중력 저하와 정신운동 지연으로 힘들어했다. 그녀는 상세한 일기와 일정 관리 앱을 계속 기록해 왔기에 스스로 이 패턴을 알아챘고, 부부간의 갈등이나 기능적 문제가 더 악화되기 전에 담당 치료사를 통해 외래 정신건강의학과 의뢰를 요청했다.
+표집된 증상 목록:
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - S031 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S035 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+  - S037 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.
+  - S038 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.
+  - S040 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F33.9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.; 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=5, 커버리지=1.0)
-  확인된 근거: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
-  누락: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F33.9)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)
+체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=5, 커버리지=1.0)
+확인된 근거:
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D008_S004_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D008_S004_P003__claude-sonnet-5_kor.xlsx
@@ -985,6 +985,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1034,11 +1039,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D008_S004_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D008_S004_P003__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.068</v>
+        <v>0.0561</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.25</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.0757</v>
+        <v>0.0633</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3026</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.3333</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
